--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -628,15 +628,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B14"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="23" min="1" max="1"/>
     <col width="108" customWidth="1" style="23" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="24">
       <c r="B2" s="25" t="inlineStr">
         <is>
@@ -651,6 +652,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="24">
       <c r="B5" s="27" t="inlineStr">
         <is>
@@ -686,6 +688,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="25.5" customHeight="1" s="24">
       <c r="B11" s="29" t="inlineStr">
         <is>
@@ -693,6 +696,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="24" customHeight="1" s="24">
       <c r="B13" s="27" t="inlineStr">
         <is>
@@ -707,10 +711,36 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -718,7 +748,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1386,9 +1416,9 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1396,7 +1426,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1420,6 +1450,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="24">
       <c r="A4" s="37" t="inlineStr">
         <is>
@@ -1561,8 +1592,8 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -152,8 +152,17 @@
       <color rgb="FFB45309"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -202,6 +211,11 @@
         <bgColor rgb="FF1F2937"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -237,7 +251,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -377,6 +391,11 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,6 +466,122 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Controls by level — lower is more durable</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Control plan'!$A$39:$A$44</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Control plan'!$B$39:$B$44</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="#,##0"/>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -750,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="23" min="1" max="1"/>
@@ -1381,6 +1516,86 @@
         <is>
           <t>A control plan whose controls are mostly level 5 and 6 has a predictable half-life. Aim for at least one level 1–3 control per root cause. And test the reaction plan once before handover — simulate a signal and confirm the reaction actually happens.</t>
         </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="47" t="inlineStr">
+        <is>
+          <t>Controls by level — how durable is this control plan?</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="48" t="inlineStr">
+        <is>
+          <t>A plan weighted towards levels 5 and 6 decays the moment attrition or a busy week arrives. Levels 1-3 survive without anyone remembering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>1 Eliminate the demand</t>
+        </is>
+      </c>
+      <c r="B39" s="49">
+        <f>COUNTIF($P$10:$P$27,LEFT(A39,1)&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>2 Design it out</t>
+        </is>
+      </c>
+      <c r="B40" s="49">
+        <f>COUNTIF($P$10:$P$27,LEFT(A40,1)&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>3 Mistake-proof it</t>
+        </is>
+      </c>
+      <c r="B41" s="49">
+        <f>COUNTIF($P$10:$P$27,LEFT(A41,1)&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>4 Automatic detection</t>
+        </is>
+      </c>
+      <c r="B42" s="49">
+        <f>COUNTIF($P$10:$P$27,LEFT(A42,1)&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>5 Standard work + training</t>
+        </is>
+      </c>
+      <c r="B43" s="49">
+        <f>COUNTIF($P$10:$P$27,LEFT(A43,1)&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>6 Reminder or awareness</t>
+        </is>
+      </c>
+      <c r="B44" s="49">
+        <f>COUNTIF($P$10:$P$27,LEFT(A44,1)&amp;"*")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1419,6 +1634,7 @@
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1450,7 +1666,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="24">
       <c r="A4" s="37" t="inlineStr">
         <is>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -162,7 +162,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -216,6 +216,11 @@
         <fgColor rgb="FFF2F7FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFAEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -251,7 +256,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -396,6 +401,15 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1055,170 +1069,434 @@
       </c>
     </row>
     <row r="10" ht="43.5" customHeight="1" s="24">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>7-day reopen rate, billing</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
-        <is>
-          <t>≤ 8.0%</t>
-        </is>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t>Warehouse query, def v2.1</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
+        <is>
+          <t>&lt;= 8.0%</t>
+        </is>
+      </c>
+      <c r="C10" s="50" t="inlineStr">
+        <is>
+          <t>Warehouse query, def v3</t>
+        </is>
+      </c>
+      <c r="D10" s="50" t="inlineStr">
         <is>
           <t>warehouse.tickets</t>
         </is>
       </c>
-      <c r="E10" s="38" t="inlineStr">
+      <c r="E10" s="50" t="inlineStr">
         <is>
           <t>Laney p' (attribute, large n)</t>
         </is>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F10" s="51" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="G10" s="39" t="n">
+      <c r="G10" s="51" t="n">
         <v>0.104</v>
       </c>
-      <c r="H10" s="39" t="n">
+      <c r="H10" s="51" t="n">
         <v>0.068</v>
       </c>
-      <c r="I10" s="38" t="inlineStr">
+      <c r="I10" s="50" t="inlineStr">
         <is>
           <t>Weekly</t>
         </is>
       </c>
-      <c r="J10" s="38" t="inlineStr">
+      <c r="J10" s="50" t="inlineStr">
         <is>
           <t>Monday ops review</t>
         </is>
       </c>
-      <c r="K10" s="38" t="inlineStr">
+      <c r="K10" s="50" t="inlineStr">
         <is>
           <t>Billing Support Mgr</t>
         </is>
       </c>
-      <c r="L10" s="38" t="inlineStr">
+      <c r="L10" s="50" t="inlineStr">
         <is>
           <t>Any point above the UCL</t>
         </is>
       </c>
-      <c r="M10" s="38" t="inlineStr">
-        <is>
-          <t>Pull 20 reopens same day, categorise causes, report Wednesday standup</t>
-        </is>
-      </c>
-      <c r="N10" s="38" t="inlineStr">
-        <is>
-          <t>Two consecutive weeks above UCL</t>
-        </is>
-      </c>
-      <c r="O10" s="38" t="inlineStr">
+      <c r="M10" s="50" t="inlineStr">
+        <is>
+          <t>Pull 20 reopens same day and classify</t>
+        </is>
+      </c>
+      <c r="N10" s="50" t="inlineStr">
+        <is>
+          <t>Two consecutive weeks above</t>
+        </is>
+      </c>
+      <c r="O10" s="50" t="inlineStr">
         <is>
           <t>Ops Director + Champion</t>
         </is>
       </c>
-      <c r="P10" s="38" t="inlineStr">
+      <c r="P10" s="50" t="inlineStr">
         <is>
           <t>2 Design it out</t>
         </is>
       </c>
-      <c r="Q10" s="38" t="inlineStr">
+      <c r="Q10" s="50" t="inlineStr">
         <is>
           <t>1 — system blocks it</t>
         </is>
       </c>
-      <c r="R10" s="38" t="inlineStr">
+      <c r="R10" s="50" t="inlineStr">
         <is>
           <t>SOP-BIL-014 v3, QA item 7</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="24">
-      <c r="A11" s="40" t="n"/>
-      <c r="B11" s="40" t="n"/>
-      <c r="C11" s="40" t="n"/>
-      <c r="D11" s="40" t="n"/>
-      <c r="E11" s="40" t="n"/>
-      <c r="F11" s="40" t="n"/>
-      <c r="G11" s="40" t="n"/>
-      <c r="H11" s="40" t="n"/>
-      <c r="I11" s="40" t="n"/>
-      <c r="J11" s="40" t="n"/>
-      <c r="K11" s="40" t="n"/>
-      <c r="L11" s="40" t="n"/>
-      <c r="M11" s="40" t="n"/>
-      <c r="N11" s="40" t="n"/>
-      <c r="O11" s="40" t="n"/>
-      <c r="P11" s="40" t="n"/>
-      <c r="Q11" s="40" t="n"/>
-      <c r="R11" s="40" t="n"/>
+      <c r="A11" s="52" t="inlineStr">
+        <is>
+          <t>Routing accuracy</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="inlineStr">
+        <is>
+          <t>&gt;= 90%</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="inlineStr">
+        <is>
+          <t>QA audit sample, 200/week</t>
+        </is>
+      </c>
+      <c r="D11" s="52" t="inlineStr">
+        <is>
+          <t>QA tool</t>
+        </is>
+      </c>
+      <c r="E11" s="52" t="inlineStr">
+        <is>
+          <t>Laney p' (attribute, large n)</t>
+        </is>
+      </c>
+      <c r="F11" s="52" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G11" s="52" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H11" s="52" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I11" s="52" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="J11" s="52" t="inlineStr">
+        <is>
+          <t>Monday ops review</t>
+        </is>
+      </c>
+      <c r="K11" s="52" t="inlineStr">
+        <is>
+          <t>Support Ops Mgr</t>
+        </is>
+      </c>
+      <c r="L11" s="52" t="inlineStr">
+        <is>
+          <t>Below the LCL, or 8 points under the centre line</t>
+        </is>
+      </c>
+      <c r="M11" s="52" t="inlineStr">
+        <is>
+          <t>Re-audit 50 tickets and review the code list</t>
+        </is>
+      </c>
+      <c r="N11" s="52" t="inlineStr">
+        <is>
+          <t>Two weeks below target</t>
+        </is>
+      </c>
+      <c r="O11" s="52" t="inlineStr">
+        <is>
+          <t>Ops Director</t>
+        </is>
+      </c>
+      <c r="P11" s="52" t="inlineStr">
+        <is>
+          <t>2 Design it out</t>
+        </is>
+      </c>
+      <c r="Q11" s="52" t="inlineStr">
+        <is>
+          <t>2 — tool warns</t>
+        </is>
+      </c>
+      <c r="R11" s="52" t="inlineStr">
+        <is>
+          <t>SOP-SUP-021 v2</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="24">
-      <c r="A12" s="40" t="n"/>
-      <c r="B12" s="40" t="n"/>
-      <c r="C12" s="40" t="n"/>
-      <c r="D12" s="40" t="n"/>
-      <c r="E12" s="40" t="n"/>
-      <c r="F12" s="40" t="n"/>
-      <c r="G12" s="40" t="n"/>
-      <c r="H12" s="40" t="n"/>
-      <c r="I12" s="40" t="n"/>
-      <c r="J12" s="40" t="n"/>
-      <c r="K12" s="40" t="n"/>
-      <c r="L12" s="40" t="n"/>
-      <c r="M12" s="40" t="n"/>
-      <c r="N12" s="40" t="n"/>
-      <c r="O12" s="40" t="n"/>
-      <c r="P12" s="40" t="n"/>
-      <c r="Q12" s="40" t="n"/>
-      <c r="R12" s="40" t="n"/>
+      <c r="A12" s="52" t="inlineStr">
+        <is>
+          <t>Nightly batch completion</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>Batch exit code</t>
+        </is>
+      </c>
+      <c r="D12" s="52" t="inlineStr">
+        <is>
+          <t>Platform monitoring</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="inlineStr">
+        <is>
+          <t>t-chart (days between failures)</t>
+        </is>
+      </c>
+      <c r="F12" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="52" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="J12" s="52" t="inlineStr">
+        <is>
+          <t>Automated alert</t>
+        </is>
+      </c>
+      <c r="K12" s="52" t="inlineStr">
+        <is>
+          <t>Platform Eng on-call</t>
+        </is>
+      </c>
+      <c r="L12" s="52" t="inlineStr">
+        <is>
+          <t>Any non-zero exit code</t>
+        </is>
+      </c>
+      <c r="M12" s="52" t="inlineStr">
+        <is>
+          <t>On-call investigates before 08:00; Billing Ops notified</t>
+        </is>
+      </c>
+      <c r="N12" s="52" t="inlineStr">
+        <is>
+          <t>Two failures in a week</t>
+        </is>
+      </c>
+      <c r="O12" s="52" t="inlineStr">
+        <is>
+          <t>Eng Manager</t>
+        </is>
+      </c>
+      <c r="P12" s="52" t="inlineStr">
+        <is>
+          <t>4 Automatic detection</t>
+        </is>
+      </c>
+      <c r="Q12" s="52" t="inlineStr">
+        <is>
+          <t>1 — system blocks it</t>
+        </is>
+      </c>
+      <c r="R12" s="52" t="inlineStr">
+        <is>
+          <t>RUN-BATCH-002</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="24">
-      <c r="A13" s="40" t="n"/>
-      <c r="B13" s="40" t="n"/>
-      <c r="C13" s="40" t="n"/>
-      <c r="D13" s="40" t="n"/>
-      <c r="E13" s="40" t="n"/>
-      <c r="F13" s="40" t="n"/>
-      <c r="G13" s="40" t="n"/>
-      <c r="H13" s="40" t="n"/>
-      <c r="I13" s="40" t="n"/>
-      <c r="J13" s="40" t="n"/>
-      <c r="K13" s="40" t="n"/>
-      <c r="L13" s="40" t="n"/>
-      <c r="M13" s="40" t="n"/>
-      <c r="N13" s="40" t="n"/>
-      <c r="O13" s="40" t="n"/>
-      <c r="P13" s="40" t="n"/>
-      <c r="Q13" s="40" t="n"/>
-      <c r="R13" s="40" t="n"/>
+      <c r="A13" s="52" t="inlineStr">
+        <is>
+          <t>Median resolution time, billing</t>
+        </is>
+      </c>
+      <c r="B13" s="52" t="inlineStr">
+        <is>
+          <t>&lt;= 4.0 h</t>
+        </is>
+      </c>
+      <c r="C13" s="52" t="inlineStr">
+        <is>
+          <t>Warehouse query, def v3</t>
+        </is>
+      </c>
+      <c r="D13" s="52" t="inlineStr">
+        <is>
+          <t>warehouse.tickets</t>
+        </is>
+      </c>
+      <c r="E13" s="52" t="inlineStr">
+        <is>
+          <t>I-MR (daily aggregate)</t>
+        </is>
+      </c>
+      <c r="F13" s="52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G13" s="52" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H13" s="52" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I13" s="52" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="J13" s="52" t="inlineStr">
+        <is>
+          <t>Daily stand-up</t>
+        </is>
+      </c>
+      <c r="K13" s="52" t="inlineStr">
+        <is>
+          <t>Billing Support Mgr</t>
+        </is>
+      </c>
+      <c r="L13" s="52" t="inlineStr">
+        <is>
+          <t>Any point above the UCL</t>
+        </is>
+      </c>
+      <c r="M13" s="52" t="inlineStr">
+        <is>
+          <t>Check queue depth and staffing for that day</t>
+        </is>
+      </c>
+      <c r="N13" s="52" t="inlineStr">
+        <is>
+          <t>Three days in a row above</t>
+        </is>
+      </c>
+      <c r="O13" s="52" t="inlineStr">
+        <is>
+          <t>Ops Director</t>
+        </is>
+      </c>
+      <c r="P13" s="52" t="inlineStr">
+        <is>
+          <t>3 Mistake-proof it</t>
+        </is>
+      </c>
+      <c r="Q13" s="52" t="inlineStr">
+        <is>
+          <t>3 — checklist step</t>
+        </is>
+      </c>
+      <c r="R13" s="52" t="inlineStr">
+        <is>
+          <t>SOP-BIL-014 v3</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="24">
-      <c r="A14" s="40" t="n"/>
-      <c r="B14" s="40" t="n"/>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="40" t="n"/>
-      <c r="E14" s="40" t="n"/>
-      <c r="F14" s="40" t="n"/>
-      <c r="G14" s="40" t="n"/>
-      <c r="H14" s="40" t="n"/>
-      <c r="I14" s="40" t="n"/>
-      <c r="J14" s="40" t="n"/>
-      <c r="K14" s="40" t="n"/>
-      <c r="L14" s="40" t="n"/>
-      <c r="M14" s="40" t="n"/>
-      <c r="N14" s="40" t="n"/>
-      <c r="O14" s="40" t="n"/>
-      <c r="P14" s="40" t="n"/>
-      <c r="Q14" s="40" t="n"/>
-      <c r="R14" s="40" t="n"/>
+      <c r="A14" s="52" t="inlineStr">
+        <is>
+          <t>Goodwill credit within authority</t>
+        </is>
+      </c>
+      <c r="B14" s="52" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>Month-end reconciliation</t>
+        </is>
+      </c>
+      <c r="D14" s="52" t="inlineStr">
+        <is>
+          <t>Finance ledger</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="inlineStr">
+        <is>
+          <t>g-chart (contacts between breaches)</t>
+        </is>
+      </c>
+      <c r="F14" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="52" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="J14" s="52" t="inlineStr">
+        <is>
+          <t>Month-end close</t>
+        </is>
+      </c>
+      <c r="K14" s="52" t="inlineStr">
+        <is>
+          <t>Finance Business Partner</t>
+        </is>
+      </c>
+      <c r="L14" s="52" t="inlineStr">
+        <is>
+          <t>Any credit above the limit</t>
+        </is>
+      </c>
+      <c r="M14" s="52" t="inlineStr">
+        <is>
+          <t>Recover or approve retrospectively; coach the agent</t>
+        </is>
+      </c>
+      <c r="N14" s="52" t="inlineStr">
+        <is>
+          <t>Two in one month</t>
+        </is>
+      </c>
+      <c r="O14" s="52" t="inlineStr">
+        <is>
+          <t>Finance Director</t>
+        </is>
+      </c>
+      <c r="P14" s="52" t="inlineStr">
+        <is>
+          <t>5 Standard work + training</t>
+        </is>
+      </c>
+      <c r="Q14" s="52" t="inlineStr">
+        <is>
+          <t>5 — nothing stops them</t>
+        </is>
+      </c>
+      <c r="R14" s="52" t="inlineStr">
+        <is>
+          <t>SOP-BIL-009 v1</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="24">
       <c r="A15" s="40" t="n"/>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -530,7 +530,12 @@
         </ser>
         <dLbls>
           <numFmt formatCode="#,##0"/>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <gapWidth val="60"/>
         <axId val="10"/>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -517,6 +517,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'Control plan'!$A$39:$A$44</f>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -510,14 +510,77 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="1F4E79"/>
-            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3F8F5A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3F8F5A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3F8F5A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'Control plan'!$A$39:$A$44</f>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="E30" s="42">
-        <f>SUMPRODUCT((A10:A26&lt;&gt;"")*((LEFT(P10:P26&amp;" ",1)="1")+(LEFT(P10:P26&amp;" ",1)="2")+(LEFT(P10:P26&amp;" ",1)="3")))</f>
+        <f>SUMPRODUCT((A10:A27&lt;&gt;"")*((LEFT(P10:P27&amp;" ",1)="1")+(LEFT(P10:P27&amp;" ",1)="2")+(LEFT(P10:P27&amp;" ",1)="3")))</f>
         <v/>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="E31" s="42">
-        <f>SUMPRODUCT((A10:A26&lt;&gt;"")*((LEFT(P10:P26&amp;" ",1)="5")+(LEFT(P10:P26&amp;" ",1)="6")))</f>
+        <f>SUMPRODUCT((A10:A27&lt;&gt;"")*((LEFT(P10:P27&amp;" ",1)="5")+(LEFT(P10:P27&amp;" ",1)="6")))</f>
         <v/>
       </c>
     </row>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -608,7 +608,7 @@
       <catAx>
         <axId val="10"/>
         <scaling>
-          <orientation val="minMax"/>
+          <orientation val="maxMin"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -608,7 +608,7 @@
       <catAx>
         <axId val="10"/>
         <scaling>
-          <orientation val="maxMin"/>
+          <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -644,9 +644,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>19</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="2880000"/>
@@ -1002,6 +1002,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="24">
       <c r="A4" s="32" t="inlineStr">
         <is>
@@ -1045,6 +1046,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="31.5" customHeight="1" s="24">
       <c r="A9" s="37" t="inlineStr">
         <is>
@@ -1807,6 +1809,7 @@
       <c r="Q26" s="40" t="n"/>
       <c r="R26" s="40" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28" ht="19.5" customHeight="1" s="24">
       <c r="A28" s="32" t="inlineStr">
         <is>
@@ -1858,6 +1861,7 @@
         <v/>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="39" customHeight="1" s="24">
       <c r="A34" s="44" t="inlineStr">
         <is>
@@ -1865,6 +1869,8 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="47" t="inlineStr">
         <is>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -256,7 +256,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -409,6 +409,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1046,7 +1049,13 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8" ht="14" customHeight="1" s="24">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>Key: UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="31.5" customHeight="1" s="24">
       <c r="A9" s="37" t="inlineStr">
         <is>
@@ -1952,7 +1961,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="B6:F6"/>
@@ -1963,6 +1972,7 @@
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A8:R8"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A34:R34"/>
   </mergeCells>
@@ -2019,6 +2029,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="24">
       <c r="A4" s="37" t="inlineStr">
         <is>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -256,7 +256,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -412,6 +412,12 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1904,6 +1910,11 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A39,1)&amp;"*")</f>
         <v/>
       </c>
+      <c r="C39" s="55" t="inlineStr">
+        <is>
+          <t>Strongest of all: the failure cannot happen because the step is gone. Retiring the manual adjustment queue counts here; a better checklist does not.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="23" t="inlineStr">
@@ -1915,6 +1926,11 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A40,1)&amp;"*")</f>
         <v/>
       </c>
+      <c r="C40" s="55" t="inlineStr">
+        <is>
+          <t>The system will not permit the failure — a ticket that cannot be closed while an adjustment is still in flight. Survives attrition, busy weeks and everyone forgetting.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
@@ -1926,6 +1942,11 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A41,1)&amp;"*")</f>
         <v/>
       </c>
+      <c r="C41" s="55" t="inlineStr">
+        <is>
+          <t>Mistake-proofing: the wrong action is blocked or corrected as it is attempted. Still durable, but it can be switched off, so name who owns the setting.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="23" t="inlineStr">
@@ -1937,6 +1958,11 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A42,1)&amp;"*")</f>
         <v/>
       </c>
+      <c r="C42" s="55" t="inlineStr">
+        <is>
+          <t>The failure still happens and something catches it without anyone looking. Useful, but you are now managing defects rather than preventing them.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="23" t="inlineStr">
@@ -1948,6 +1974,11 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A43,1)&amp;"*")</f>
         <v/>
       </c>
+      <c r="C43" s="55" t="inlineStr">
+        <is>
+          <t>Depends on a person remembering. Decays with every new hire and every busy week — count these honestly rather than relying on them.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="23" t="inlineStr">
@@ -1958,6 +1989,11 @@
       <c r="B44" s="49">
         <f>COUNTIF($P$10:$P$27,LEFT(A44,1)&amp;"*")</f>
         <v/>
+      </c>
+      <c r="C44" s="55" t="inlineStr">
+        <is>
+          <t>A briefing, a poster, a line in the wiki. Half-life measured in weeks. If most of your controls sit here, the process will drift back after handover.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -256,7 +256,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -412,6 +412,72 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1910,7 +1976,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A39,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C39" s="55" t="inlineStr">
+      <c r="C39" s="77" t="inlineStr">
         <is>
           <t>Strongest of all: the failure cannot happen because the step is gone. Retiring the manual adjustment queue counts here; a better checklist does not.</t>
         </is>
@@ -1926,7 +1992,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A40,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C40" s="55" t="inlineStr">
+      <c r="C40" s="77" t="inlineStr">
         <is>
           <t>The system will not permit the failure — a ticket that cannot be closed while an adjustment is still in flight. Survives attrition, busy weeks and everyone forgetting.</t>
         </is>
@@ -1942,7 +2008,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A41,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C41" s="55" t="inlineStr">
+      <c r="C41" s="77" t="inlineStr">
         <is>
           <t>Mistake-proofing: the wrong action is blocked or corrected as it is attempted. Still durable, but it can be switched off, so name who owns the setting.</t>
         </is>
@@ -1958,7 +2024,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A42,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C42" s="55" t="inlineStr">
+      <c r="C42" s="77" t="inlineStr">
         <is>
           <t>The failure still happens and something catches it without anyone looking. Useful, but you are now managing defects rather than preventing them.</t>
         </is>
@@ -1974,7 +2040,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A43,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C43" s="55" t="inlineStr">
+      <c r="C43" s="77" t="inlineStr">
         <is>
           <t>Depends on a person remembering. Decays with every new hire and every busy week — count these honestly rather than relying on them.</t>
         </is>
@@ -1990,7 +2056,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A44,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C44" s="55" t="inlineStr">
+      <c r="C44" s="77" t="inlineStr">
         <is>
           <t>A briefing, a poster, a line in the wiki. Half-life measured in weeks. If most of your controls sit here, the process will drift back after handover.</t>
         </is>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -162,7 +162,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -221,6 +221,11 @@
         <fgColor rgb="FFECFAEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9E3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -256,7 +261,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -484,6 +489,15 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1112,12 +1126,12 @@
     <row r="7" ht="15" customHeight="1" s="24">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t>Row 1 example</t>
+          <t>Green cells</t>
         </is>
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>A realistic worked example, so you can see the expected format. Delete or overwrite it.</t>
+          <t>A realistic worked example, so you can see the expected format and the sheet is not blank when you open it. Replace it with your own.</t>
         </is>
       </c>
     </row>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -261,7 +261,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -498,6 +498,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1064,8 +1067,10 @@
     <col width="16" customWidth="1" style="23" min="2" max="2"/>
     <col width="26" customWidth="1" style="23" min="3" max="3"/>
     <col width="20" customWidth="1" style="23" min="4" max="5"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
     <col width="12" customWidth="1" style="23" min="6" max="6"/>
     <col width="10" customWidth="1" style="23" min="7" max="8"/>
+    <col width="13" customWidth="1" style="24" min="8" max="8"/>
     <col width="12" customWidth="1" style="23" min="9" max="9"/>
     <col width="22" customWidth="1" style="23" min="10" max="10"/>
     <col width="16" customWidth="1" style="23" min="11" max="11"/>
@@ -1073,6 +1078,7 @@
     <col width="42" customWidth="1" style="23" min="13" max="13"/>
     <col width="24" customWidth="1" style="23" min="14" max="14"/>
     <col width="18" customWidth="1" style="23" min="15" max="16"/>
+    <col width="13" customWidth="1" style="24" min="16" max="16"/>
     <col width="20" customWidth="1" style="23" min="17" max="17"/>
     <col width="26" customWidth="1" style="23" min="18" max="18"/>
   </cols>
@@ -1973,14 +1979,14 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="48" t="inlineStr">
+    <row r="38" ht="13" customHeight="1" s="24">
+      <c r="A38" s="81" t="inlineStr">
         <is>
           <t>A plan weighted towards levels 5 and 6 decays the moment attrition or a busy week arrives. Levels 1-3 survive without anyone remembering.</t>
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="13" customHeight="1" s="24">
       <c r="A39" s="23" t="inlineStr">
         <is>
           <t>1 Eliminate the demand</t>
@@ -1990,13 +1996,13 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A39,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C39" s="77" t="inlineStr">
+      <c r="C39" s="81" t="inlineStr">
         <is>
           <t>Strongest of all: the failure cannot happen because the step is gone. Retiring the manual adjustment queue counts here; a better checklist does not.</t>
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="13" customHeight="1" s="24">
       <c r="A40" s="23" t="inlineStr">
         <is>
           <t>2 Design it out</t>
@@ -2006,13 +2012,13 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A40,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C40" s="77" t="inlineStr">
+      <c r="C40" s="81" t="inlineStr">
         <is>
           <t>The system will not permit the failure — a ticket that cannot be closed while an adjustment is still in flight. Survives attrition, busy weeks and everyone forgetting.</t>
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="13" customHeight="1" s="24">
       <c r="A41" s="23" t="inlineStr">
         <is>
           <t>3 Mistake-proof it</t>
@@ -2022,13 +2028,13 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A41,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C41" s="77" t="inlineStr">
+      <c r="C41" s="81" t="inlineStr">
         <is>
           <t>Mistake-proofing: the wrong action is blocked or corrected as it is attempted. Still durable, but it can be switched off, so name who owns the setting.</t>
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="13" customHeight="1" s="24">
       <c r="A42" s="23" t="inlineStr">
         <is>
           <t>4 Automatic detection</t>
@@ -2038,13 +2044,13 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A42,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C42" s="77" t="inlineStr">
+      <c r="C42" s="81" t="inlineStr">
         <is>
           <t>The failure still happens and something catches it without anyone looking. Useful, but you are now managing defects rather than preventing them.</t>
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="13" customHeight="1" s="24">
       <c r="A43" s="23" t="inlineStr">
         <is>
           <t>5 Standard work + training</t>
@@ -2054,13 +2060,13 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A43,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C43" s="77" t="inlineStr">
+      <c r="C43" s="81" t="inlineStr">
         <is>
           <t>Depends on a person remembering. Decays with every new hire and every busy week — count these honestly rather than relying on them.</t>
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="13" customHeight="1" s="24">
       <c r="A44" s="23" t="inlineStr">
         <is>
           <t>6 Reminder or awareness</t>
@@ -2070,27 +2076,34 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A44,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C44" s="77" t="inlineStr">
+      <c r="C44" s="81" t="inlineStr">
         <is>
           <t>A briefing, a poster, a line in the wiki. Half-life measured in weeks. If most of your controls sit here, the process will drift back after handover.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="20">
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="C39:R39"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B6:F6"/>
     <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A28:R28"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A1:R1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A8:R8"/>
+    <mergeCell ref="C42:R42"/>
+    <mergeCell ref="A38:R38"/>
+    <mergeCell ref="A28:R28"/>
+    <mergeCell ref="A34:R34"/>
+    <mergeCell ref="C41:R41"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="C44:R44"/>
+    <mergeCell ref="C40:R40"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="C43:R43"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A34:R34"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="E10:E26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -261,7 +261,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -501,6 +501,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1996,7 +1999,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A39,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C39" s="81" t="inlineStr">
+      <c r="C39" s="82" t="inlineStr">
         <is>
           <t>Strongest of all: the failure cannot happen because the step is gone. Retiring the manual adjustment queue counts here; a better checklist does not.</t>
         </is>
@@ -2012,7 +2015,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A40,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C40" s="81" t="inlineStr">
+      <c r="C40" s="82" t="inlineStr">
         <is>
           <t>The system will not permit the failure — a ticket that cannot be closed while an adjustment is still in flight. Survives attrition, busy weeks and everyone forgetting.</t>
         </is>
@@ -2028,7 +2031,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A41,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C41" s="81" t="inlineStr">
+      <c r="C41" s="82" t="inlineStr">
         <is>
           <t>Mistake-proofing: the wrong action is blocked or corrected as it is attempted. Still durable, but it can be switched off, so name who owns the setting.</t>
         </is>
@@ -2044,7 +2047,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A42,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C42" s="81" t="inlineStr">
+      <c r="C42" s="82" t="inlineStr">
         <is>
           <t>The failure still happens and something catches it without anyone looking. Useful, but you are now managing defects rather than preventing them.</t>
         </is>
@@ -2060,7 +2063,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A43,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C43" s="81" t="inlineStr">
+      <c r="C43" s="82" t="inlineStr">
         <is>
           <t>Depends on a person remembering. Decays with every new hire and every busy week — count these honestly rather than relying on them.</t>
         </is>
@@ -2076,7 +2079,7 @@
         <f>COUNTIF($P$10:$P$27,LEFT(A44,1)&amp;"*")</f>
         <v/>
       </c>
-      <c r="C44" s="81" t="inlineStr">
+      <c r="C44" s="82" t="inlineStr">
         <is>
           <t>A briefing, a poster, a line in the wiki. Half-life measured in weeks. If most of your controls sit here, the process will drift back after handover.</t>
         </is>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -1147,7 +1147,7 @@
     <row r="8" ht="14" customHeight="1" s="24">
       <c r="A8" s="53" t="inlineStr">
         <is>
-          <t>Key: UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
+          <t xml:space="preserve">  ·  Key: UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
         </is>
       </c>
     </row>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -1144,10 +1144,10 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="14" customHeight="1" s="24">
+    <row r="8" ht="60" customHeight="1" s="24">
       <c r="A8" s="53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ·  Key: UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
+          <t xml:space="preserve">  ·  Key: Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
         </is>
       </c>
     </row>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -1144,10 +1144,14 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="24">
+    <row r="8" ht="132" customHeight="1" s="24">
       <c r="A8" s="53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ·  Key: Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
+          <t xml:space="preserve">  ·  Key:
+• Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved
+• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line  ·  Key:
+• Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved
+• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
         </is>
       </c>
     </row>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -161,6 +161,11 @@
       <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -261,7 +266,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -504,6 +509,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1063,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R44"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="23" min="1" max="1"/>
@@ -1144,10 +1152,14 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="132" customHeight="1" s="24">
+    <row r="8" ht="252" customHeight="1" s="24">
       <c r="A8" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">  ·  Key:
+• Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved
+• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line  ·  Key:
+• Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved
+• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line  ·  Key:
 • Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved
 • UCL / LCL = upper and lower control limits, ±3 sigma from the centre line  ·  Key:
 • Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved
@@ -2089,8 +2101,26 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55" ht="55" customHeight="1" s="24">
+      <c r="E55" s="83" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Level 1 eliminates the demand, level 6 asks someone to be careful. A plan weighted to the right will decay: training and reminders fade within two quarters, and the process reverts with nobody accountable for noticing. Count the bars on the left before you sign it off.
+SO:  If the plan is weighted right, send it back. Convert at least the top-RPN controls to level 1 or 2 before signing off, because training and reminders fade inside two quarters and the process reverts with nobody accountable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C39:R39"/>
     <mergeCell ref="A29:D29"/>
@@ -2104,6 +2134,7 @@
     <mergeCell ref="A28:R28"/>
     <mergeCell ref="A34:R34"/>
     <mergeCell ref="C41:R41"/>
+    <mergeCell ref="E55:M55"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="C44:R44"/>
     <mergeCell ref="C40:R40"/>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -1152,16 +1152,10 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="252" customHeight="1" s="24">
+    <row r="8" ht="72" customHeight="1" s="24">
       <c r="A8" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">  ·  Key:
-• Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved
-• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line  ·  Key:
-• Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved
-• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line  ·  Key:
-• Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved
-• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line  ·  Key:
 • Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved
 • UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
         </is>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -266,7 +266,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -511,6 +511,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1034,8 +1037,20 @@
     </row>
     <row r="15"/>
     <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
+    <row r="17" ht="26" customHeight="1" s="24">
+      <c r="A17" s="84" t="inlineStr">
+        <is>
+          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1" s="24">
+      <c r="A18" s="83" t="inlineStr">
+        <is>
+          <t>Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved</t>
+        </is>
+      </c>
+    </row>
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
@@ -1059,6 +1074,10 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1152,11 +1171,11 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="72" customHeight="1" s="24">
+    <row r="8" ht="36" customHeight="1" s="24">
       <c r="A8" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">  ·  Key:
-• Centre line = the average the chart is drawn around, frozen from the baseline window and then held still. On the I-MR sheet it is 415.05 seconds from the first twenty points (B6). Held still is what makes it useful: recomputing it as new data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved
+• Centre line = the average the chart is drawn around, frozen from the baseline window and then held still.
 • UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
         </is>
       </c>

--- a/templates/17-control-plan.xlsx
+++ b/templates/17-control-plan.xlsx
@@ -1171,12 +1171,12 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1" s="24">
+    <row r="8" ht="60" customHeight="1" s="24">
       <c r="A8" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">  ·  Key:
 • Centre line = the average the chart is drawn around, frozen from the baseline window and then held still.
-• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
+• UCL / LCL = upper and lower control limits, a fixed number of standard errors either side of the centre line — ±3 sigma where each point is plotted on its own, and narrower on EWMA or CUSUM, where the statistic already averages several periods and so varies less than a single point does</t>
         </is>
       </c>
     </row>
